--- a/Apostas_Diarias/Apostas_20260406.xlsx
+++ b/Apostas_Diarias/Apostas_20260406.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/21df80ec97692de0/Documentos/GitHub/ARKAD_PROD/Apostas_Diarias/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="10" documentId="11_2B590F4F95C64702F1A0D8F0505CB8774431F8D7" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{900C975D-7559-458B-82FA-F621D0D9F32E}"/>
+  <xr:revisionPtr revIDLastSave="12" documentId="11_2B590F4F95A6C6437103C7F05041A8B05063E65E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9636256F-DBCD-4002-9A90-17B44FBE1EA6}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="43">
   <si>
     <t>Data</t>
   </si>
@@ -77,10 +77,10 @@
     <t>07:15:00</t>
   </si>
   <si>
-    <t>NETHERLANDS 2</t>
-  </si>
-  <si>
-    <t>Helmond Sport x RKC Waalwijk</t>
+    <t>POLAND 1</t>
+  </si>
+  <si>
+    <t>Nieciecza x Piast Gliwice</t>
   </si>
   <si>
     <t>Lay_CS_0x1_B365</t>
@@ -107,13 +107,61 @@
     <t>ITALY 2</t>
   </si>
   <si>
+    <t>Catanzaro x AC Monza</t>
+  </si>
+  <si>
     <t>Reggiana x Pescara</t>
   </si>
   <si>
-    <t>13:00:00</t>
-  </si>
-  <si>
-    <t>Viborg x AGF</t>
+    <t>12:00:00</t>
+  </si>
+  <si>
+    <t>NORWAY 1</t>
+  </si>
+  <si>
+    <t>Ham-Kam x Brann</t>
+  </si>
+  <si>
+    <t>12:15:00</t>
+  </si>
+  <si>
+    <t>Sampdoria x Empoli</t>
+  </si>
+  <si>
+    <t>14:00:00</t>
+  </si>
+  <si>
+    <t>TURKEY 1</t>
+  </si>
+  <si>
+    <t>Kocaelispor x Basaksehir</t>
+  </si>
+  <si>
+    <t>20:00:00</t>
+  </si>
+  <si>
+    <t>PARAGUAY 1</t>
+  </si>
+  <si>
+    <t>Sportivo Trinidense x Rubio Nu</t>
+  </si>
+  <si>
+    <t>21:00:00</t>
+  </si>
+  <si>
+    <t>BRAZIL 2</t>
+  </si>
+  <si>
+    <t>Goias x Criciuma</t>
+  </si>
+  <si>
+    <t>P2</t>
+  </si>
+  <si>
+    <t>PORTUGAL 2</t>
+  </si>
+  <si>
+    <t>Porto B x Chaves</t>
   </si>
 </sst>
 </file>
@@ -453,14 +501,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L6"/>
+  <dimension ref="A1:L12"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="2" width="8" customWidth="1"/>
     <col min="3" max="3" width="12" customWidth="1"/>
     <col min="4" max="4" width="17" customWidth="1"/>
-    <col min="5" max="5" width="32" customWidth="1"/>
+    <col min="5" max="5" width="34" customWidth="1"/>
     <col min="6" max="6" width="19" customWidth="1"/>
     <col min="7" max="7" width="12" customWidth="1"/>
     <col min="8" max="8" width="17" customWidth="1"/>
@@ -503,6 +551,9 @@
       <c r="K1" t="s">
         <v>10</v>
       </c>
+      <c r="L1">
+        <v>500</v>
+      </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
@@ -524,12 +575,14 @@
         <v>16</v>
       </c>
       <c r="G2">
-        <v>13.5</v>
+        <v>10.5</v>
       </c>
       <c r="H2">
-        <v>13.5</v>
+        <f>G2</f>
+        <v>10.5</v>
       </c>
       <c r="I2">
+        <f>$L$1</f>
         <v>500</v>
       </c>
       <c r="J2" t="str">
@@ -538,7 +591,7 @@
       </c>
       <c r="K2">
         <f>IF(L2=1,0.935/(H2-1)*I2,-500)</f>
-        <v>37.400000000000006</v>
+        <v>49.210526315789473</v>
       </c>
       <c r="L2">
         <v>1</v>
@@ -567,17 +620,19 @@
         <v>11.5</v>
       </c>
       <c r="H3">
+        <f t="shared" ref="H3:H12" si="0">G3</f>
         <v>11.5</v>
       </c>
       <c r="I3">
+        <f t="shared" ref="I3:I12" si="1">$L$1</f>
         <v>500</v>
       </c>
       <c r="J3" t="str">
-        <f t="shared" ref="J3:J6" si="0">IF(L3=1,"GREEN","RED")</f>
+        <f t="shared" ref="J3:J12" si="2">IF(L3=1,"GREEN","RED")</f>
         <v>GREEN</v>
       </c>
       <c r="K3">
-        <f t="shared" ref="K3:K6" si="1">IF(L3=1,0.935/(H3-1)*I3,-500)</f>
+        <f t="shared" ref="K3:K12" si="3">IF(L3=1,0.935/(H3-1)*I3,-500)</f>
         <v>44.523809523809526</v>
       </c>
       <c r="L3">
@@ -607,17 +662,19 @@
         <v>11</v>
       </c>
       <c r="H4">
+        <f t="shared" si="0"/>
         <v>11</v>
       </c>
       <c r="I4">
+        <f t="shared" si="1"/>
         <v>500</v>
       </c>
       <c r="J4" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>GREEN</v>
       </c>
       <c r="K4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>46.75</v>
       </c>
       <c r="L4">
@@ -644,21 +701,23 @@
         <v>16</v>
       </c>
       <c r="G5">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="H5">
-        <v>10.5</v>
+        <f t="shared" si="0"/>
+        <v>11</v>
       </c>
       <c r="I5">
+        <f t="shared" si="1"/>
         <v>500</v>
       </c>
       <c r="J5" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>GREEN</v>
       </c>
       <c r="K5">
-        <f t="shared" si="1"/>
-        <v>49.210526315789473</v>
+        <f t="shared" si="3"/>
+        <v>46.75</v>
       </c>
       <c r="L5">
         <v>1</v>
@@ -672,35 +731,289 @@
         <v>12</v>
       </c>
       <c r="C6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" t="s">
+        <v>23</v>
+      </c>
+      <c r="E6" t="s">
         <v>25</v>
-      </c>
-      <c r="D6" t="s">
-        <v>20</v>
-      </c>
-      <c r="E6" t="s">
-        <v>26</v>
       </c>
       <c r="F6" t="s">
         <v>16</v>
       </c>
       <c r="G6">
+        <v>10.5</v>
+      </c>
+      <c r="H6">
+        <f t="shared" si="0"/>
+        <v>10.5</v>
+      </c>
+      <c r="I6">
+        <f t="shared" si="1"/>
+        <v>500</v>
+      </c>
+      <c r="J6" t="str">
+        <f t="shared" si="2"/>
+        <v>GREEN</v>
+      </c>
+      <c r="K6">
+        <f t="shared" si="3"/>
+        <v>49.210526315789473</v>
+      </c>
+      <c r="L6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" t="s">
         <v>12</v>
       </c>
-      <c r="H6">
+      <c r="C7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7" t="s">
+        <v>27</v>
+      </c>
+      <c r="E7" t="s">
+        <v>28</v>
+      </c>
+      <c r="F7" t="s">
+        <v>16</v>
+      </c>
+      <c r="G7">
+        <v>10.5</v>
+      </c>
+      <c r="H7">
+        <f t="shared" si="0"/>
+        <v>10.5</v>
+      </c>
+      <c r="I7">
+        <f t="shared" si="1"/>
+        <v>500</v>
+      </c>
+      <c r="J7" t="str">
+        <f t="shared" si="2"/>
+        <v>GREEN</v>
+      </c>
+      <c r="K7">
+        <f t="shared" si="3"/>
+        <v>49.210526315789473</v>
+      </c>
+      <c r="L7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" t="s">
         <v>12</v>
       </c>
-      <c r="I6">
-        <v>500</v>
-      </c>
-      <c r="J6" t="str">
+      <c r="C8" t="s">
+        <v>29</v>
+      </c>
+      <c r="D8" t="s">
+        <v>23</v>
+      </c>
+      <c r="E8" t="s">
+        <v>30</v>
+      </c>
+      <c r="F8" t="s">
+        <v>16</v>
+      </c>
+      <c r="G8">
+        <v>11</v>
+      </c>
+      <c r="H8">
         <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="I8">
+        <f t="shared" si="1"/>
+        <v>500</v>
+      </c>
+      <c r="J8" t="str">
+        <f t="shared" si="2"/>
         <v>GREEN</v>
       </c>
-      <c r="K6">
+      <c r="K8">
+        <f t="shared" si="3"/>
+        <v>46.75</v>
+      </c>
+      <c r="L8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>11</v>
+      </c>
+      <c r="B9" t="s">
+        <v>12</v>
+      </c>
+      <c r="C9" t="s">
+        <v>31</v>
+      </c>
+      <c r="D9" t="s">
+        <v>32</v>
+      </c>
+      <c r="E9" t="s">
+        <v>33</v>
+      </c>
+      <c r="F9" t="s">
+        <v>16</v>
+      </c>
+      <c r="G9">
+        <v>9.8000000000000007</v>
+      </c>
+      <c r="H9">
+        <f t="shared" si="0"/>
+        <v>9.8000000000000007</v>
+      </c>
+      <c r="I9">
         <f t="shared" si="1"/>
-        <v>42.5</v>
-      </c>
-      <c r="L6">
+        <v>500</v>
+      </c>
+      <c r="J9" t="str">
+        <f t="shared" si="2"/>
+        <v>GREEN</v>
+      </c>
+      <c r="K9">
+        <f t="shared" si="3"/>
+        <v>53.125</v>
+      </c>
+      <c r="L9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C10" t="s">
+        <v>34</v>
+      </c>
+      <c r="D10" t="s">
+        <v>35</v>
+      </c>
+      <c r="E10" t="s">
+        <v>36</v>
+      </c>
+      <c r="F10" t="s">
+        <v>16</v>
+      </c>
+      <c r="G10">
+        <v>11</v>
+      </c>
+      <c r="H10">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="I10">
+        <f t="shared" si="1"/>
+        <v>500</v>
+      </c>
+      <c r="J10" t="str">
+        <f t="shared" si="2"/>
+        <v>GREEN</v>
+      </c>
+      <c r="K10">
+        <f t="shared" si="3"/>
+        <v>46.75</v>
+      </c>
+      <c r="L10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>11</v>
+      </c>
+      <c r="B11" t="s">
+        <v>12</v>
+      </c>
+      <c r="C11" t="s">
+        <v>37</v>
+      </c>
+      <c r="D11" t="s">
+        <v>38</v>
+      </c>
+      <c r="E11" t="s">
+        <v>39</v>
+      </c>
+      <c r="F11" t="s">
+        <v>16</v>
+      </c>
+      <c r="G11">
+        <v>11.5</v>
+      </c>
+      <c r="H11">
+        <f t="shared" si="0"/>
+        <v>11.5</v>
+      </c>
+      <c r="I11">
+        <f t="shared" si="1"/>
+        <v>500</v>
+      </c>
+      <c r="J11" t="str">
+        <f t="shared" si="2"/>
+        <v>GREEN</v>
+      </c>
+      <c r="K11">
+        <f t="shared" si="3"/>
+        <v>44.523809523809526</v>
+      </c>
+      <c r="L11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>11</v>
+      </c>
+      <c r="B12" t="s">
+        <v>40</v>
+      </c>
+      <c r="C12" t="s">
+        <v>31</v>
+      </c>
+      <c r="D12" t="s">
+        <v>41</v>
+      </c>
+      <c r="E12" t="s">
+        <v>42</v>
+      </c>
+      <c r="F12" t="s">
+        <v>16</v>
+      </c>
+      <c r="G12">
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="H12">
+        <f t="shared" si="0"/>
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="I12">
+        <f t="shared" si="1"/>
+        <v>500</v>
+      </c>
+      <c r="J12" t="str">
+        <f t="shared" si="2"/>
+        <v>GREEN</v>
+      </c>
+      <c r="K12">
+        <f t="shared" si="3"/>
+        <v>59.935897435897431</v>
+      </c>
+      <c r="L12">
         <v>1</v>
       </c>
     </row>

--- a/Apostas_Diarias/Apostas_20260406.xlsx
+++ b/Apostas_Diarias/Apostas_20260406.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/21df80ec97692de0/Documentos/GitHub/ARKAD_PROD/Apostas_Diarias/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="12" documentId="11_2B590F4F95A6C6437103C7F05041A8B05063E65E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9636256F-DBCD-4002-9A90-17B44FBE1EA6}"/>
+  <xr:revisionPtr revIDLastSave="49" documentId="11_07B98F4295A647159983C8F0505ED87656CDF7C8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4277A67D-A443-4B0E-8481-453F622FC521}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="78">
   <si>
     <t>Data</t>
   </si>
@@ -77,13 +77,31 @@
     <t>07:15:00</t>
   </si>
   <si>
+    <t>NETHERLANDS 2</t>
+  </si>
+  <si>
+    <t>Helmond Sport x RKC Waalwijk</t>
+  </si>
+  <si>
+    <t>Lay_CS_0x1_B365</t>
+  </si>
+  <si>
     <t>POLAND 1</t>
   </si>
   <si>
     <t>Nieciecza x Piast Gliwice</t>
   </si>
   <si>
-    <t>Lay_CS_0x1_B365</t>
+    <t>07:30:00</t>
+  </si>
+  <si>
+    <t>ITALY 3</t>
+  </si>
+  <si>
+    <t>FC Giugliano x Crotone</t>
+  </si>
+  <si>
+    <t>Sorrento x Team Altamura</t>
   </si>
   <si>
     <t>09:00:00</t>
@@ -95,24 +113,66 @@
     <t>Grasshoppers Zurich x Sion</t>
   </si>
   <si>
+    <t>SWITZERLAND 2</t>
+  </si>
+  <si>
+    <t>Stade Nyonnais x Yverdon Sport</t>
+  </si>
+  <si>
     <t>DENMARK 1</t>
   </si>
   <si>
     <t>Vejle x Randers</t>
   </si>
   <si>
+    <t>AUSTRIA 2</t>
+  </si>
+  <si>
+    <t>WSC Hertha Wels x SV Austria Salzburg</t>
+  </si>
+  <si>
+    <t>09:30:00</t>
+  </si>
+  <si>
+    <t>NORWAY 2</t>
+  </si>
+  <si>
+    <t>Asane x Moss</t>
+  </si>
+  <si>
+    <t>Aurora Pro Patria 1919 x Triestina</t>
+  </si>
+  <si>
+    <t>Giana Erminio x SSD Dolomiti Bellunesi</t>
+  </si>
+  <si>
+    <t>Salernitana x Benevento</t>
+  </si>
+  <si>
     <t>10:00:00</t>
   </si>
   <si>
     <t>ITALY 2</t>
   </si>
   <si>
-    <t>Catanzaro x AC Monza</t>
-  </si>
-  <si>
     <t>Reggiana x Pescara</t>
   </si>
   <si>
+    <t>SWEDEN 2</t>
+  </si>
+  <si>
+    <t>Varbergs BoIS x Ostersunds FK</t>
+  </si>
+  <si>
+    <t>11:30:00</t>
+  </si>
+  <si>
+    <t>ROMANIA 1</t>
+  </si>
+  <si>
+    <t>ACS Petrolul 52 x Csikszereda</t>
+  </si>
+  <si>
     <t>12:00:00</t>
   </si>
   <si>
@@ -122,10 +182,22 @@
     <t>Ham-Kam x Brann</t>
   </si>
   <si>
-    <t>12:15:00</t>
-  </si>
-  <si>
-    <t>Sampdoria x Empoli</t>
+    <t>12:30:00</t>
+  </si>
+  <si>
+    <t>Albinoleffe x Pergolettese</t>
+  </si>
+  <si>
+    <t>13:00:00</t>
+  </si>
+  <si>
+    <t>IRELAND 2</t>
+  </si>
+  <si>
+    <t>Athlone Town x Longford</t>
+  </si>
+  <si>
+    <t>Viborg x AGF</t>
   </si>
   <si>
     <t>14:00:00</t>
@@ -137,13 +209,22 @@
     <t>Kocaelispor x Basaksehir</t>
   </si>
   <si>
-    <t>20:00:00</t>
-  </si>
-  <si>
-    <t>PARAGUAY 1</t>
-  </si>
-  <si>
-    <t>Sportivo Trinidense x Rubio Nu</t>
+    <t>14:30:00</t>
+  </si>
+  <si>
+    <t>ISRAEL 1</t>
+  </si>
+  <si>
+    <t>Hapoel Tel Aviv x Maccabi Haifa</t>
+  </si>
+  <si>
+    <t>16:45:00</t>
+  </si>
+  <si>
+    <t>PORTUGAL 1</t>
+  </si>
+  <si>
+    <t>Casa Pia x Benfica</t>
   </si>
   <si>
     <t>21:00:00</t>
@@ -155,6 +236,21 @@
     <t>Goias x Criciuma</t>
   </si>
   <si>
+    <t>CHILE 1</t>
+  </si>
+  <si>
+    <t>Huachipato x Univ de Concepcion</t>
+  </si>
+  <si>
+    <t>21:15:00</t>
+  </si>
+  <si>
+    <t>ARGENTINA 1</t>
+  </si>
+  <si>
+    <t>Instituto x Defensa y Justicia</t>
+  </si>
+  <si>
     <t>P2</t>
   </si>
   <si>
@@ -162,6 +258,15 @@
   </si>
   <si>
     <t>Porto B x Chaves</t>
+  </si>
+  <si>
+    <t>P3</t>
+  </si>
+  <si>
+    <t>Lay_CS_1x0_B365</t>
+  </si>
+  <si>
+    <t>P4</t>
   </si>
 </sst>
 </file>
@@ -501,14 +606,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L12"/>
+  <dimension ref="A1:L44"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="2" width="8" customWidth="1"/>
     <col min="3" max="3" width="12" customWidth="1"/>
     <col min="4" max="4" width="17" customWidth="1"/>
-    <col min="5" max="5" width="34" customWidth="1"/>
+    <col min="5" max="5" width="40" customWidth="1"/>
     <col min="6" max="6" width="19" customWidth="1"/>
     <col min="7" max="7" width="12" customWidth="1"/>
     <col min="8" max="8" width="17" customWidth="1"/>
@@ -551,9 +656,6 @@
       <c r="K1" t="s">
         <v>10</v>
       </c>
-      <c r="L1">
-        <v>500</v>
-      </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
@@ -563,26 +665,24 @@
         <v>12</v>
       </c>
       <c r="C2" t="s">
-        <v>13</v>
+        <v>43</v>
       </c>
       <c r="D2" t="s">
-        <v>14</v>
+        <v>44</v>
       </c>
       <c r="E2" t="s">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="F2" t="s">
         <v>16</v>
       </c>
       <c r="G2">
-        <v>10.5</v>
+        <v>15.5</v>
       </c>
       <c r="H2">
-        <f>G2</f>
-        <v>10.5</v>
+        <v>15.5</v>
       </c>
       <c r="I2">
-        <f>$L$1</f>
         <v>500</v>
       </c>
       <c r="J2" t="str">
@@ -591,7 +691,7 @@
       </c>
       <c r="K2">
         <f>IF(L2=1,0.935/(H2-1)*I2,-500)</f>
-        <v>49.210526315789473</v>
+        <v>32.241379310344826</v>
       </c>
       <c r="L2">
         <v>1</v>
@@ -602,38 +702,36 @@
         <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>12</v>
+        <v>75</v>
       </c>
       <c r="C3" t="s">
-        <v>17</v>
+        <v>43</v>
       </c>
       <c r="D3" t="s">
-        <v>18</v>
+        <v>44</v>
       </c>
       <c r="E3" t="s">
-        <v>19</v>
+        <v>45</v>
       </c>
       <c r="F3" t="s">
-        <v>16</v>
+        <v>76</v>
       </c>
       <c r="G3">
-        <v>11.5</v>
+        <v>7.4</v>
       </c>
       <c r="H3">
-        <f t="shared" ref="H3:H12" si="0">G3</f>
-        <v>11.5</v>
+        <v>7.4</v>
       </c>
       <c r="I3">
-        <f t="shared" ref="I3:I12" si="1">$L$1</f>
         <v>500</v>
       </c>
       <c r="J3" t="str">
-        <f t="shared" ref="J3:J12" si="2">IF(L3=1,"GREEN","RED")</f>
+        <f t="shared" ref="J3:J44" si="0">IF(L3=1,"GREEN","RED")</f>
         <v>GREEN</v>
       </c>
       <c r="K3">
-        <f t="shared" ref="K3:K12" si="3">IF(L3=1,0.935/(H3-1)*I3,-500)</f>
-        <v>44.523809523809526</v>
+        <f t="shared" ref="K3:K44" si="1">IF(L3=1,0.935/(H3-1)*I3,-500)</f>
+        <v>73.046875</v>
       </c>
       <c r="L3">
         <v>1</v>
@@ -647,35 +745,33 @@
         <v>12</v>
       </c>
       <c r="C4" t="s">
-        <v>17</v>
+        <v>49</v>
       </c>
       <c r="D4" t="s">
         <v>20</v>
       </c>
       <c r="E4" t="s">
-        <v>21</v>
+        <v>50</v>
       </c>
       <c r="F4" t="s">
         <v>16</v>
       </c>
       <c r="G4">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="H4">
-        <f t="shared" si="0"/>
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="I4">
-        <f t="shared" si="1"/>
         <v>500</v>
       </c>
       <c r="J4" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>GREEN</v>
       </c>
       <c r="K4">
-        <f t="shared" si="3"/>
-        <v>46.75</v>
+        <f t="shared" si="1"/>
+        <v>44.523809523809526</v>
       </c>
       <c r="L4">
         <v>1</v>
@@ -686,38 +782,36 @@
         <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>12</v>
+        <v>75</v>
       </c>
       <c r="C5" t="s">
-        <v>22</v>
+        <v>49</v>
       </c>
       <c r="D5" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="E5" t="s">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="F5" t="s">
-        <v>16</v>
+        <v>76</v>
       </c>
       <c r="G5">
-        <v>11</v>
+        <v>6.4</v>
       </c>
       <c r="H5">
-        <f t="shared" si="0"/>
-        <v>11</v>
+        <v>6.4</v>
       </c>
       <c r="I5">
-        <f t="shared" si="1"/>
         <v>500</v>
       </c>
       <c r="J5" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>GREEN</v>
       </c>
       <c r="K5">
-        <f t="shared" si="3"/>
-        <v>46.75</v>
+        <f t="shared" si="1"/>
+        <v>86.574074074074062</v>
       </c>
       <c r="L5">
         <v>1</v>
@@ -731,35 +825,33 @@
         <v>12</v>
       </c>
       <c r="C6" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="D6" t="s">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="E6" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="F6" t="s">
         <v>16</v>
       </c>
       <c r="G6">
-        <v>10.5</v>
+        <v>13</v>
       </c>
       <c r="H6">
-        <f t="shared" si="0"/>
-        <v>10.5</v>
+        <v>13</v>
       </c>
       <c r="I6">
-        <f t="shared" si="1"/>
         <v>500</v>
       </c>
       <c r="J6" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>GREEN</v>
       </c>
       <c r="K6">
-        <f t="shared" si="3"/>
-        <v>49.210526315789473</v>
+        <f t="shared" si="1"/>
+        <v>38.958333333333336</v>
       </c>
       <c r="L6">
         <v>1</v>
@@ -770,38 +862,36 @@
         <v>11</v>
       </c>
       <c r="B7" t="s">
-        <v>12</v>
+        <v>77</v>
       </c>
       <c r="C7" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="D7" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="E7" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="F7" t="s">
-        <v>16</v>
+        <v>76</v>
       </c>
       <c r="G7">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="H7">
-        <f t="shared" si="0"/>
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="I7">
-        <f t="shared" si="1"/>
         <v>500</v>
       </c>
       <c r="J7" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>GREEN</v>
       </c>
       <c r="K7">
-        <f t="shared" si="3"/>
-        <v>49.210526315789473</v>
+        <f t="shared" si="1"/>
+        <v>40.652173913043484</v>
       </c>
       <c r="L7">
         <v>1</v>
@@ -815,35 +905,33 @@
         <v>12</v>
       </c>
       <c r="C8" t="s">
-        <v>29</v>
+        <v>51</v>
       </c>
       <c r="D8" t="s">
-        <v>23</v>
+        <v>52</v>
       </c>
       <c r="E8" t="s">
-        <v>30</v>
+        <v>53</v>
       </c>
       <c r="F8" t="s">
         <v>16</v>
       </c>
       <c r="G8">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H8">
-        <f t="shared" si="0"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I8">
-        <f t="shared" si="1"/>
         <v>500</v>
       </c>
       <c r="J8" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>GREEN</v>
       </c>
       <c r="K8">
-        <f t="shared" si="3"/>
-        <v>46.75</v>
+        <f t="shared" si="1"/>
+        <v>42.5</v>
       </c>
       <c r="L8">
         <v>1</v>
@@ -854,37 +942,35 @@
         <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>12</v>
+        <v>77</v>
       </c>
       <c r="C9" t="s">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="D9" t="s">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="E9" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="F9" t="s">
-        <v>16</v>
+        <v>76</v>
       </c>
       <c r="G9">
         <v>9.8000000000000007</v>
       </c>
       <c r="H9">
-        <f t="shared" si="0"/>
         <v>9.8000000000000007</v>
       </c>
       <c r="I9">
-        <f t="shared" si="1"/>
         <v>500</v>
       </c>
       <c r="J9" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>GREEN</v>
       </c>
       <c r="K9">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>53.125</v>
       </c>
       <c r="L9">
@@ -899,35 +985,33 @@
         <v>12</v>
       </c>
       <c r="C10" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D10" t="s">
+        <v>20</v>
+      </c>
+      <c r="E10" t="s">
         <v>35</v>
       </c>
-      <c r="E10" t="s">
-        <v>36</v>
-      </c>
       <c r="F10" t="s">
         <v>16</v>
       </c>
       <c r="G10">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H10">
-        <f t="shared" si="0"/>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I10">
-        <f t="shared" si="1"/>
         <v>500</v>
       </c>
       <c r="J10" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>GREEN</v>
       </c>
       <c r="K10">
-        <f t="shared" si="3"/>
-        <v>46.75</v>
+        <f t="shared" si="1"/>
+        <v>51.944444444444443</v>
       </c>
       <c r="L10">
         <v>1</v>
@@ -938,38 +1022,36 @@
         <v>11</v>
       </c>
       <c r="B11" t="s">
-        <v>12</v>
+        <v>77</v>
       </c>
       <c r="C11" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D11" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="E11" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="F11" t="s">
-        <v>16</v>
+        <v>76</v>
       </c>
       <c r="G11">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="H11">
-        <f t="shared" si="0"/>
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="I11">
-        <f t="shared" si="1"/>
         <v>500</v>
       </c>
       <c r="J11" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>GREEN</v>
       </c>
       <c r="K11">
-        <f t="shared" si="3"/>
-        <v>44.523809523809526</v>
+        <f t="shared" si="1"/>
+        <v>42.5</v>
       </c>
       <c r="L11">
         <v>1</v>
@@ -980,44 +1062,1325 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
+        <v>12</v>
+      </c>
+      <c r="C12" t="s">
+        <v>61</v>
+      </c>
+      <c r="D12" t="s">
+        <v>62</v>
+      </c>
+      <c r="E12" t="s">
+        <v>63</v>
+      </c>
+      <c r="F12" t="s">
+        <v>16</v>
+      </c>
+      <c r="G12">
+        <v>10.5</v>
+      </c>
+      <c r="H12">
+        <v>10.5</v>
+      </c>
+      <c r="I12">
+        <v>500</v>
+      </c>
+      <c r="J12" t="str">
+        <f t="shared" si="0"/>
+        <v>GREEN</v>
+      </c>
+      <c r="K12">
+        <f t="shared" si="1"/>
+        <v>49.210526315789473</v>
+      </c>
+      <c r="L12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>11</v>
+      </c>
+      <c r="B13" t="s">
+        <v>12</v>
+      </c>
+      <c r="C13" t="s">
+        <v>19</v>
+      </c>
+      <c r="D13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F13" t="s">
+        <v>16</v>
+      </c>
+      <c r="G13">
+        <v>11</v>
+      </c>
+      <c r="H13">
+        <v>11</v>
+      </c>
+      <c r="I13">
+        <v>500</v>
+      </c>
+      <c r="J13" t="str">
+        <f t="shared" si="0"/>
+        <v>GREEN</v>
+      </c>
+      <c r="K13">
+        <f t="shared" si="1"/>
+        <v>46.75</v>
+      </c>
+      <c r="L13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>11</v>
+      </c>
+      <c r="B14" t="s">
+        <v>77</v>
+      </c>
+      <c r="C14" t="s">
+        <v>19</v>
+      </c>
+      <c r="D14" t="s">
+        <v>20</v>
+      </c>
+      <c r="E14" t="s">
+        <v>21</v>
+      </c>
+      <c r="F14" t="s">
+        <v>76</v>
+      </c>
+      <c r="G14">
+        <v>13.5</v>
+      </c>
+      <c r="H14">
+        <v>13.5</v>
+      </c>
+      <c r="I14">
+        <v>500</v>
+      </c>
+      <c r="J14" t="str">
+        <f t="shared" si="0"/>
+        <v>RED</v>
+      </c>
+      <c r="K14">
+        <f t="shared" si="1"/>
+        <v>-500</v>
+      </c>
+      <c r="L14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>11</v>
+      </c>
+      <c r="B15" t="s">
+        <v>12</v>
+      </c>
+      <c r="C15" t="s">
+        <v>32</v>
+      </c>
+      <c r="D15" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" t="s">
+        <v>36</v>
+      </c>
+      <c r="F15" t="s">
+        <v>16</v>
+      </c>
+      <c r="G15">
+        <v>14</v>
+      </c>
+      <c r="H15">
+        <v>14</v>
+      </c>
+      <c r="I15">
+        <v>500</v>
+      </c>
+      <c r="J15" t="str">
+        <f t="shared" si="0"/>
+        <v>GREEN</v>
+      </c>
+      <c r="K15">
+        <f t="shared" si="1"/>
+        <v>35.96153846153846</v>
+      </c>
+      <c r="L15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>11</v>
+      </c>
+      <c r="B16" t="s">
+        <v>75</v>
+      </c>
+      <c r="C16" t="s">
+        <v>32</v>
+      </c>
+      <c r="D16" t="s">
+        <v>20</v>
+      </c>
+      <c r="E16" t="s">
+        <v>36</v>
+      </c>
+      <c r="F16" t="s">
+        <v>76</v>
+      </c>
+      <c r="G16">
+        <v>7.8</v>
+      </c>
+      <c r="H16">
+        <v>7.8</v>
+      </c>
+      <c r="I16">
+        <v>500</v>
+      </c>
+      <c r="J16" t="str">
+        <f t="shared" si="0"/>
+        <v>GREEN</v>
+      </c>
+      <c r="K16">
+        <f t="shared" si="1"/>
+        <v>68.75</v>
+      </c>
+      <c r="L16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>11</v>
+      </c>
+      <c r="B17" t="s">
+        <v>12</v>
+      </c>
+      <c r="C17" t="s">
+        <v>64</v>
+      </c>
+      <c r="D17" t="s">
+        <v>65</v>
+      </c>
+      <c r="E17" t="s">
+        <v>66</v>
+      </c>
+      <c r="F17" t="s">
+        <v>16</v>
+      </c>
+      <c r="G17">
+        <v>11.5</v>
+      </c>
+      <c r="H17">
+        <v>11.5</v>
+      </c>
+      <c r="I17">
+        <v>500</v>
+      </c>
+      <c r="J17" t="str">
+        <f t="shared" si="0"/>
+        <v>GREEN</v>
+      </c>
+      <c r="K17">
+        <f t="shared" si="1"/>
+        <v>44.523809523809526</v>
+      </c>
+      <c r="L17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>11</v>
+      </c>
+      <c r="B18" t="s">
+        <v>75</v>
+      </c>
+      <c r="C18" t="s">
+        <v>64</v>
+      </c>
+      <c r="D18" t="s">
+        <v>65</v>
+      </c>
+      <c r="E18" t="s">
+        <v>66</v>
+      </c>
+      <c r="F18" t="s">
+        <v>76</v>
+      </c>
+      <c r="G18">
+        <v>7.2</v>
+      </c>
+      <c r="H18">
+        <v>7.2</v>
+      </c>
+      <c r="I18">
+        <v>500</v>
+      </c>
+      <c r="J18" t="str">
+        <f t="shared" si="0"/>
+        <v>RED</v>
+      </c>
+      <c r="K18">
+        <f t="shared" si="1"/>
+        <v>-500</v>
+      </c>
+      <c r="L18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>11</v>
+      </c>
+      <c r="B19" t="s">
+        <v>12</v>
+      </c>
+      <c r="C19" t="s">
+        <v>23</v>
+      </c>
+      <c r="D19" t="s">
+        <v>24</v>
+      </c>
+      <c r="E19" t="s">
+        <v>25</v>
+      </c>
+      <c r="F19" t="s">
+        <v>16</v>
+      </c>
+      <c r="G19">
+        <v>11.5</v>
+      </c>
+      <c r="H19">
+        <v>11.5</v>
+      </c>
+      <c r="I19">
+        <v>500</v>
+      </c>
+      <c r="J19" t="str">
+        <f t="shared" si="0"/>
+        <v>GREEN</v>
+      </c>
+      <c r="K19">
+        <f t="shared" si="1"/>
+        <v>44.523809523809526</v>
+      </c>
+      <c r="L19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>11</v>
+      </c>
+      <c r="B20" t="s">
+        <v>12</v>
+      </c>
+      <c r="C20" t="s">
+        <v>46</v>
+      </c>
+      <c r="D20" t="s">
+        <v>47</v>
+      </c>
+      <c r="E20" t="s">
+        <v>48</v>
+      </c>
+      <c r="F20" t="s">
+        <v>16</v>
+      </c>
+      <c r="G20">
+        <v>10.5</v>
+      </c>
+      <c r="H20">
+        <v>10.5</v>
+      </c>
+      <c r="I20">
+        <v>500</v>
+      </c>
+      <c r="J20" t="str">
+        <f t="shared" si="0"/>
+        <v>GREEN</v>
+      </c>
+      <c r="K20">
+        <f t="shared" si="1"/>
+        <v>49.210526315789473</v>
+      </c>
+      <c r="L20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>11</v>
+      </c>
+      <c r="B21" t="s">
+        <v>12</v>
+      </c>
+      <c r="C21" t="s">
+        <v>58</v>
+      </c>
+      <c r="D21" t="s">
+        <v>59</v>
+      </c>
+      <c r="E21" t="s">
+        <v>60</v>
+      </c>
+      <c r="F21" t="s">
+        <v>16</v>
+      </c>
+      <c r="G21">
+        <v>14.5</v>
+      </c>
+      <c r="H21">
+        <v>14.5</v>
+      </c>
+      <c r="I21">
+        <v>500</v>
+      </c>
+      <c r="J21" t="str">
+        <f t="shared" si="0"/>
+        <v>GREEN</v>
+      </c>
+      <c r="K21">
+        <f t="shared" si="1"/>
+        <v>34.629629629629626</v>
+      </c>
+      <c r="L21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>11</v>
+      </c>
+      <c r="B22" t="s">
+        <v>77</v>
+      </c>
+      <c r="C22" t="s">
+        <v>58</v>
+      </c>
+      <c r="D22" t="s">
+        <v>59</v>
+      </c>
+      <c r="E22" t="s">
+        <v>60</v>
+      </c>
+      <c r="F22" t="s">
+        <v>76</v>
+      </c>
+      <c r="G22">
+        <v>15</v>
+      </c>
+      <c r="H22">
+        <v>15</v>
+      </c>
+      <c r="I22">
+        <v>500</v>
+      </c>
+      <c r="J22" t="str">
+        <f t="shared" si="0"/>
+        <v>GREEN</v>
+      </c>
+      <c r="K22">
+        <f t="shared" si="1"/>
+        <v>33.392857142857146</v>
+      </c>
+      <c r="L22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>11</v>
+      </c>
+      <c r="B23" t="s">
+        <v>12</v>
+      </c>
+      <c r="C23" t="s">
+        <v>13</v>
+      </c>
+      <c r="D23" t="s">
+        <v>14</v>
+      </c>
+      <c r="E23" t="s">
+        <v>15</v>
+      </c>
+      <c r="F23" t="s">
+        <v>16</v>
+      </c>
+      <c r="G23">
+        <v>13.5</v>
+      </c>
+      <c r="H23">
+        <v>13.5</v>
+      </c>
+      <c r="I23">
+        <v>500</v>
+      </c>
+      <c r="J23" t="str">
+        <f t="shared" si="0"/>
+        <v>GREEN</v>
+      </c>
+      <c r="K23">
+        <f t="shared" si="1"/>
+        <v>37.400000000000006</v>
+      </c>
+      <c r="L23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>11</v>
+      </c>
+      <c r="B24" t="s">
+        <v>12</v>
+      </c>
+      <c r="C24" t="s">
+        <v>64</v>
+      </c>
+      <c r="D24" t="s">
+        <v>67</v>
+      </c>
+      <c r="E24" t="s">
+        <v>68</v>
+      </c>
+      <c r="F24" t="s">
+        <v>16</v>
+      </c>
+      <c r="G24">
+        <v>12.5</v>
+      </c>
+      <c r="H24">
+        <v>12.5</v>
+      </c>
+      <c r="I24">
+        <v>500</v>
+      </c>
+      <c r="J24" t="str">
+        <f t="shared" si="0"/>
+        <v>GREEN</v>
+      </c>
+      <c r="K24">
+        <f t="shared" si="1"/>
+        <v>40.652173913043484</v>
+      </c>
+      <c r="L24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>11</v>
+      </c>
+      <c r="B25" t="s">
+        <v>77</v>
+      </c>
+      <c r="C25" t="s">
+        <v>64</v>
+      </c>
+      <c r="D25" t="s">
+        <v>67</v>
+      </c>
+      <c r="E25" t="s">
+        <v>68</v>
+      </c>
+      <c r="F25" t="s">
+        <v>76</v>
+      </c>
+      <c r="G25">
+        <v>10.5</v>
+      </c>
+      <c r="H25">
+        <v>10.5</v>
+      </c>
+      <c r="I25">
+        <v>500</v>
+      </c>
+      <c r="J25" t="str">
+        <f t="shared" si="0"/>
+        <v>GREEN</v>
+      </c>
+      <c r="K25">
+        <f t="shared" si="1"/>
+        <v>49.210526315789473</v>
+      </c>
+      <c r="L25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>11</v>
+      </c>
+      <c r="B26" t="s">
+        <v>12</v>
+      </c>
+      <c r="C26" t="s">
+        <v>69</v>
+      </c>
+      <c r="D26" t="s">
+        <v>70</v>
+      </c>
+      <c r="E26" t="s">
+        <v>71</v>
+      </c>
+      <c r="F26" t="s">
+        <v>16</v>
+      </c>
+      <c r="G26">
+        <v>11.5</v>
+      </c>
+      <c r="H26">
+        <v>11.5</v>
+      </c>
+      <c r="I26">
+        <v>500</v>
+      </c>
+      <c r="J26" t="str">
+        <f t="shared" si="0"/>
+        <v>GREEN</v>
+      </c>
+      <c r="K26">
+        <f t="shared" si="1"/>
+        <v>44.523809523809526</v>
+      </c>
+      <c r="L26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>11</v>
+      </c>
+      <c r="B27" t="s">
+        <v>75</v>
+      </c>
+      <c r="C27" t="s">
+        <v>69</v>
+      </c>
+      <c r="D27" t="s">
+        <v>70</v>
+      </c>
+      <c r="E27" t="s">
+        <v>71</v>
+      </c>
+      <c r="F27" t="s">
+        <v>76</v>
+      </c>
+      <c r="G27">
+        <v>7.2</v>
+      </c>
+      <c r="H27">
+        <v>7.2</v>
+      </c>
+      <c r="I27">
+        <v>500</v>
+      </c>
+      <c r="J27" t="str">
+        <f t="shared" si="0"/>
+        <v>GREEN</v>
+      </c>
+      <c r="K27">
+        <f t="shared" si="1"/>
+        <v>75.403225806451616</v>
+      </c>
+      <c r="L27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>11</v>
+      </c>
+      <c r="B28" t="s">
+        <v>12</v>
+      </c>
+      <c r="C28" t="s">
+        <v>55</v>
+      </c>
+      <c r="D28" t="s">
+        <v>56</v>
+      </c>
+      <c r="E28" t="s">
+        <v>57</v>
+      </c>
+      <c r="F28" t="s">
+        <v>16</v>
+      </c>
+      <c r="G28">
+        <v>9.8000000000000007</v>
+      </c>
+      <c r="H28">
+        <v>9.8000000000000007</v>
+      </c>
+      <c r="I28">
+        <v>500</v>
+      </c>
+      <c r="J28" t="str">
+        <f t="shared" si="0"/>
+        <v>GREEN</v>
+      </c>
+      <c r="K28">
+        <f t="shared" si="1"/>
+        <v>53.125</v>
+      </c>
+      <c r="L28">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>11</v>
+      </c>
+      <c r="B29" t="s">
+        <v>77</v>
+      </c>
+      <c r="C29" t="s">
+        <v>55</v>
+      </c>
+      <c r="D29" t="s">
+        <v>56</v>
+      </c>
+      <c r="E29" t="s">
+        <v>57</v>
+      </c>
+      <c r="F29" t="s">
+        <v>76</v>
+      </c>
+      <c r="G29">
+        <v>13</v>
+      </c>
+      <c r="H29">
+        <v>13</v>
+      </c>
+      <c r="I29">
+        <v>500</v>
+      </c>
+      <c r="J29" t="str">
+        <f t="shared" si="0"/>
+        <v>GREEN</v>
+      </c>
+      <c r="K29">
+        <f t="shared" si="1"/>
+        <v>38.958333333333336</v>
+      </c>
+      <c r="L29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>11</v>
+      </c>
+      <c r="B30" t="s">
+        <v>12</v>
+      </c>
+      <c r="C30" t="s">
+        <v>13</v>
+      </c>
+      <c r="D30" t="s">
+        <v>17</v>
+      </c>
+      <c r="E30" t="s">
+        <v>18</v>
+      </c>
+      <c r="F30" t="s">
+        <v>16</v>
+      </c>
+      <c r="G30">
+        <v>10.5</v>
+      </c>
+      <c r="H30">
+        <v>10.5</v>
+      </c>
+      <c r="I30">
+        <v>500</v>
+      </c>
+      <c r="J30" t="str">
+        <f t="shared" si="0"/>
+        <v>GREEN</v>
+      </c>
+      <c r="K30">
+        <f t="shared" si="1"/>
+        <v>49.210526315789473</v>
+      </c>
+      <c r="L30">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>11</v>
+      </c>
+      <c r="B31" t="s">
+        <v>77</v>
+      </c>
+      <c r="C31" t="s">
+        <v>13</v>
+      </c>
+      <c r="D31" t="s">
+        <v>17</v>
+      </c>
+      <c r="E31" t="s">
+        <v>18</v>
+      </c>
+      <c r="F31" t="s">
+        <v>76</v>
+      </c>
+      <c r="G31">
+        <v>14</v>
+      </c>
+      <c r="H31">
+        <v>14</v>
+      </c>
+      <c r="I31">
+        <v>500</v>
+      </c>
+      <c r="J31" t="str">
+        <f t="shared" si="0"/>
+        <v>GREEN</v>
+      </c>
+      <c r="K31">
+        <f t="shared" si="1"/>
+        <v>35.96153846153846</v>
+      </c>
+      <c r="L31">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>11</v>
+      </c>
+      <c r="B32" t="s">
+        <v>72</v>
+      </c>
+      <c r="C32" t="s">
+        <v>55</v>
+      </c>
+      <c r="D32" t="s">
+        <v>73</v>
+      </c>
+      <c r="E32" t="s">
+        <v>74</v>
+      </c>
+      <c r="F32" t="s">
+        <v>16</v>
+      </c>
+      <c r="G32">
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="H32">
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="I32">
+        <v>500</v>
+      </c>
+      <c r="J32" t="str">
+        <f t="shared" si="0"/>
+        <v>GREEN</v>
+      </c>
+      <c r="K32">
+        <f t="shared" si="1"/>
+        <v>59.935897435897431</v>
+      </c>
+      <c r="L32">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>11</v>
+      </c>
+      <c r="B33" t="s">
+        <v>77</v>
+      </c>
+      <c r="C33" t="s">
+        <v>55</v>
+      </c>
+      <c r="D33" t="s">
+        <v>73</v>
+      </c>
+      <c r="E33" t="s">
+        <v>74</v>
+      </c>
+      <c r="F33" t="s">
+        <v>76</v>
+      </c>
+      <c r="G33">
+        <v>11.5</v>
+      </c>
+      <c r="H33">
+        <v>11.5</v>
+      </c>
+      <c r="I33">
+        <v>500</v>
+      </c>
+      <c r="J33" t="str">
+        <f t="shared" si="0"/>
+        <v>GREEN</v>
+      </c>
+      <c r="K33">
+        <f t="shared" si="1"/>
+        <v>44.523809523809526</v>
+      </c>
+      <c r="L33">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>11</v>
+      </c>
+      <c r="B34" t="s">
+        <v>12</v>
+      </c>
+      <c r="C34" t="s">
+        <v>38</v>
+      </c>
+      <c r="D34" t="s">
+        <v>39</v>
+      </c>
+      <c r="E34" t="s">
         <v>40</v>
       </c>
-      <c r="C12" t="s">
+      <c r="F34" t="s">
+        <v>16</v>
+      </c>
+      <c r="G34">
+        <v>10.5</v>
+      </c>
+      <c r="H34">
+        <v>10.5</v>
+      </c>
+      <c r="I34">
+        <v>500</v>
+      </c>
+      <c r="J34" t="str">
+        <f t="shared" si="0"/>
+        <v>GREEN</v>
+      </c>
+      <c r="K34">
+        <f t="shared" si="1"/>
+        <v>49.210526315789473</v>
+      </c>
+      <c r="L34">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>11</v>
+      </c>
+      <c r="B35" t="s">
+        <v>12</v>
+      </c>
+      <c r="C35" t="s">
+        <v>32</v>
+      </c>
+      <c r="D35" t="s">
+        <v>20</v>
+      </c>
+      <c r="E35" t="s">
+        <v>37</v>
+      </c>
+      <c r="F35" t="s">
+        <v>16</v>
+      </c>
+      <c r="G35">
+        <v>9.4</v>
+      </c>
+      <c r="H35">
+        <v>9.4</v>
+      </c>
+      <c r="I35">
+        <v>500</v>
+      </c>
+      <c r="J35" t="str">
+        <f t="shared" si="0"/>
+        <v>RED</v>
+      </c>
+      <c r="K35">
+        <f t="shared" si="1"/>
+        <v>-500</v>
+      </c>
+      <c r="L35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>11</v>
+      </c>
+      <c r="B36" t="s">
+        <v>12</v>
+      </c>
+      <c r="C36" t="s">
+        <v>19</v>
+      </c>
+      <c r="D36" t="s">
+        <v>20</v>
+      </c>
+      <c r="E36" t="s">
+        <v>22</v>
+      </c>
+      <c r="F36" t="s">
+        <v>16</v>
+      </c>
+      <c r="G36">
+        <v>13.5</v>
+      </c>
+      <c r="H36">
+        <v>13.5</v>
+      </c>
+      <c r="I36">
+        <v>500</v>
+      </c>
+      <c r="J36" t="str">
+        <f t="shared" si="0"/>
+        <v>GREEN</v>
+      </c>
+      <c r="K36">
+        <f t="shared" si="1"/>
+        <v>37.400000000000006</v>
+      </c>
+      <c r="L36">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>11</v>
+      </c>
+      <c r="B37" t="s">
+        <v>75</v>
+      </c>
+      <c r="C37" t="s">
+        <v>19</v>
+      </c>
+      <c r="D37" t="s">
+        <v>20</v>
+      </c>
+      <c r="E37" t="s">
+        <v>22</v>
+      </c>
+      <c r="F37" t="s">
+        <v>76</v>
+      </c>
+      <c r="G37">
+        <v>7.6</v>
+      </c>
+      <c r="H37">
+        <v>7.6</v>
+      </c>
+      <c r="I37">
+        <v>500</v>
+      </c>
+      <c r="J37" t="str">
+        <f t="shared" si="0"/>
+        <v>GREEN</v>
+      </c>
+      <c r="K37">
+        <f t="shared" si="1"/>
+        <v>70.833333333333343</v>
+      </c>
+      <c r="L37">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>11</v>
+      </c>
+      <c r="B38" t="s">
+        <v>12</v>
+      </c>
+      <c r="C38" t="s">
+        <v>23</v>
+      </c>
+      <c r="D38" t="s">
+        <v>26</v>
+      </c>
+      <c r="E38" t="s">
+        <v>27</v>
+      </c>
+      <c r="F38" t="s">
+        <v>16</v>
+      </c>
+      <c r="G38">
+        <v>11.5</v>
+      </c>
+      <c r="H38">
+        <v>11.5</v>
+      </c>
+      <c r="I38">
+        <v>500</v>
+      </c>
+      <c r="J38" t="str">
+        <f t="shared" si="0"/>
+        <v>GREEN</v>
+      </c>
+      <c r="K38">
+        <f t="shared" si="1"/>
+        <v>44.523809523809526</v>
+      </c>
+      <c r="L38">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>11</v>
+      </c>
+      <c r="B39" t="s">
+        <v>12</v>
+      </c>
+      <c r="C39" t="s">
+        <v>38</v>
+      </c>
+      <c r="D39" t="s">
+        <v>41</v>
+      </c>
+      <c r="E39" t="s">
+        <v>42</v>
+      </c>
+      <c r="F39" t="s">
+        <v>16</v>
+      </c>
+      <c r="G39">
+        <v>12</v>
+      </c>
+      <c r="H39">
+        <v>12</v>
+      </c>
+      <c r="I39">
+        <v>500</v>
+      </c>
+      <c r="J39" t="str">
+        <f t="shared" si="0"/>
+        <v>GREEN</v>
+      </c>
+      <c r="K39">
+        <f t="shared" si="1"/>
+        <v>42.5</v>
+      </c>
+      <c r="L39">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>11</v>
+      </c>
+      <c r="B40" t="s">
+        <v>75</v>
+      </c>
+      <c r="C40" t="s">
+        <v>38</v>
+      </c>
+      <c r="D40" t="s">
+        <v>41</v>
+      </c>
+      <c r="E40" t="s">
+        <v>42</v>
+      </c>
+      <c r="F40" t="s">
+        <v>76</v>
+      </c>
+      <c r="G40">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="H40">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="I40">
+        <v>500</v>
+      </c>
+      <c r="J40" t="str">
+        <f t="shared" si="0"/>
+        <v>GREEN</v>
+      </c>
+      <c r="K40">
+        <f t="shared" si="1"/>
+        <v>64.930555555555557</v>
+      </c>
+      <c r="L40">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>11</v>
+      </c>
+      <c r="B41" t="s">
+        <v>12</v>
+      </c>
+      <c r="C41" t="s">
+        <v>23</v>
+      </c>
+      <c r="D41" t="s">
+        <v>28</v>
+      </c>
+      <c r="E41" t="s">
+        <v>29</v>
+      </c>
+      <c r="F41" t="s">
+        <v>16</v>
+      </c>
+      <c r="G41">
+        <v>11</v>
+      </c>
+      <c r="H41">
+        <v>11</v>
+      </c>
+      <c r="I41">
+        <v>500</v>
+      </c>
+      <c r="J41" t="str">
+        <f t="shared" si="0"/>
+        <v>GREEN</v>
+      </c>
+      <c r="K41">
+        <f t="shared" si="1"/>
+        <v>46.75</v>
+      </c>
+      <c r="L41">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>11</v>
+      </c>
+      <c r="B42" t="s">
+        <v>77</v>
+      </c>
+      <c r="C42" t="s">
+        <v>23</v>
+      </c>
+      <c r="D42" t="s">
+        <v>28</v>
+      </c>
+      <c r="E42" t="s">
+        <v>29</v>
+      </c>
+      <c r="F42" t="s">
+        <v>76</v>
+      </c>
+      <c r="G42">
+        <v>13.5</v>
+      </c>
+      <c r="H42">
+        <v>13.5</v>
+      </c>
+      <c r="I42">
+        <v>500</v>
+      </c>
+      <c r="J42" t="str">
+        <f t="shared" si="0"/>
+        <v>GREEN</v>
+      </c>
+      <c r="K42">
+        <f t="shared" si="1"/>
+        <v>37.400000000000006</v>
+      </c>
+      <c r="L42">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
+        <v>11</v>
+      </c>
+      <c r="B43" t="s">
+        <v>12</v>
+      </c>
+      <c r="C43" t="s">
+        <v>51</v>
+      </c>
+      <c r="D43" t="s">
+        <v>28</v>
+      </c>
+      <c r="E43" t="s">
+        <v>54</v>
+      </c>
+      <c r="F43" t="s">
+        <v>16</v>
+      </c>
+      <c r="G43">
+        <v>12</v>
+      </c>
+      <c r="H43">
+        <v>12</v>
+      </c>
+      <c r="I43">
+        <v>500</v>
+      </c>
+      <c r="J43" t="str">
+        <f t="shared" si="0"/>
+        <v>GREEN</v>
+      </c>
+      <c r="K43">
+        <f t="shared" si="1"/>
+        <v>42.5</v>
+      </c>
+      <c r="L43">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
+        <v>11</v>
+      </c>
+      <c r="B44" t="s">
+        <v>12</v>
+      </c>
+      <c r="C44" t="s">
+        <v>23</v>
+      </c>
+      <c r="D44" t="s">
+        <v>30</v>
+      </c>
+      <c r="E44" t="s">
         <v>31</v>
       </c>
-      <c r="D12" t="s">
-        <v>41</v>
-      </c>
-      <c r="E12" t="s">
-        <v>42</v>
-      </c>
-      <c r="F12" t="s">
-        <v>16</v>
-      </c>
-      <c r="G12">
-        <v>8.8000000000000007</v>
-      </c>
-      <c r="H12">
-        <f t="shared" si="0"/>
-        <v>8.8000000000000007</v>
-      </c>
-      <c r="I12">
-        <f t="shared" si="1"/>
-        <v>500</v>
-      </c>
-      <c r="J12" t="str">
-        <f t="shared" si="2"/>
-        <v>GREEN</v>
-      </c>
-      <c r="K12">
-        <f t="shared" si="3"/>
-        <v>59.935897435897431</v>
-      </c>
-      <c r="L12">
+      <c r="F44" t="s">
+        <v>16</v>
+      </c>
+      <c r="G44">
+        <v>13</v>
+      </c>
+      <c r="H44">
+        <v>13</v>
+      </c>
+      <c r="I44">
+        <v>500</v>
+      </c>
+      <c r="J44" t="str">
+        <f t="shared" si="0"/>
+        <v>GREEN</v>
+      </c>
+      <c r="K44">
+        <f t="shared" si="1"/>
+        <v>38.958333333333336</v>
+      </c>
+      <c r="L44">
         <v>1</v>
       </c>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K44">
+    <sortCondition ref="E2:E44"/>
+  </sortState>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>